--- a/ios-reports/latest/Excel/Passed_Test_Cases.xlsx
+++ b/ios-reports/latest/Excel/Passed_Test_Cases.xlsx
@@ -1703,7 +1703,7 @@
         <v>6</v>
       </c>
       <c r="D2" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1717,7 +1717,7 @@
         <v>7</v>
       </c>
       <c r="D3" s="3">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1913,7 +1913,7 @@
         <v>21</v>
       </c>
       <c r="D17" s="3">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1983,7 +1983,7 @@
         <v>26</v>
       </c>
       <c r="D22" s="2">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -2011,7 +2011,7 @@
         <v>28</v>
       </c>
       <c r="D24" s="2">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -2403,7 +2403,7 @@
         <v>58</v>
       </c>
       <c r="D52" s="2">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -2767,7 +2767,7 @@
         <v>84</v>
       </c>
       <c r="D78" s="2">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -2781,7 +2781,7 @@
         <v>85</v>
       </c>
       <c r="D79" s="3">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3145,7 +3145,7 @@
         <v>113</v>
       </c>
       <c r="D105" s="3">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="106" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3355,7 +3355,7 @@
         <v>128</v>
       </c>
       <c r="D120" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="121" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3397,7 +3397,7 @@
         <v>131</v>
       </c>
       <c r="D123" s="3">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="124" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3439,7 +3439,7 @@
         <v>134</v>
       </c>
       <c r="D126" s="2">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3509,7 +3509,7 @@
         <v>139</v>
       </c>
       <c r="D131" s="3">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3565,7 +3565,7 @@
         <v>143</v>
       </c>
       <c r="D135" s="3">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="136" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3705,7 +3705,7 @@
         <v>153</v>
       </c>
       <c r="D145" s="3">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="146" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3803,7 +3803,7 @@
         <v>162</v>
       </c>
       <c r="D152" s="2">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="153" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3957,7 +3957,7 @@
         <v>173</v>
       </c>
       <c r="D163" s="3">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="164" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3985,7 +3985,7 @@
         <v>175</v>
       </c>
       <c r="D165" s="3">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="166" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -4167,7 +4167,7 @@
         <v>188</v>
       </c>
       <c r="D178" s="2">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="179" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -4223,7 +4223,7 @@
         <v>192</v>
       </c>
       <c r="D182" s="2">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="183" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -4363,7 +4363,7 @@
         <v>202</v>
       </c>
       <c r="D192" s="2">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="193" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -4447,7 +4447,7 @@
         <v>208</v>
       </c>
       <c r="D198" s="2">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="199" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -4475,7 +4475,7 @@
         <v>210</v>
       </c>
       <c r="D200" s="2">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="201" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -4503,7 +4503,7 @@
         <v>214</v>
       </c>
       <c r="D202" s="2">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="203" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -4517,7 +4517,7 @@
         <v>215</v>
       </c>
       <c r="D203" s="3">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="204" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -4685,7 +4685,7 @@
         <v>227</v>
       </c>
       <c r="D215" s="3">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="216" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -4797,7 +4797,7 @@
         <v>235</v>
       </c>
       <c r="D223" s="3">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="224" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -4909,7 +4909,7 @@
         <v>243</v>
       </c>
       <c r="D231" s="3">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="232" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -5567,7 +5567,7 @@
         <v>292</v>
       </c>
       <c r="D278" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="279" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -5581,7 +5581,7 @@
         <v>293</v>
       </c>
       <c r="D279" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="280" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6029,7 +6029,7 @@
         <v>325</v>
       </c>
       <c r="D311" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="312" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6267,7 +6267,7 @@
         <v>342</v>
       </c>
       <c r="D328" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="329" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6771,7 +6771,7 @@
         <v>378</v>
       </c>
       <c r="D364" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="365" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6855,7 +6855,7 @@
         <v>384</v>
       </c>
       <c r="D370" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="371" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6883,7 +6883,7 @@
         <v>386</v>
       </c>
       <c r="D372" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="373" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6911,7 +6911,7 @@
         <v>388</v>
       </c>
       <c r="D374" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="375" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -7191,7 +7191,7 @@
         <v>408</v>
       </c>
       <c r="D394" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="395" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -7261,7 +7261,7 @@
         <v>413</v>
       </c>
       <c r="D399" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="400" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">

--- a/ios-reports/latest/Excel/Passed_Test_Cases.xlsx
+++ b/ios-reports/latest/Excel/Passed_Test_Cases.xlsx
@@ -1717,7 +1717,7 @@
         <v>7</v>
       </c>
       <c r="D3" s="3">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -2011,7 +2011,7 @@
         <v>28</v>
       </c>
       <c r="D24" s="2">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -2683,7 +2683,7 @@
         <v>78</v>
       </c>
       <c r="D72" s="2">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -2767,7 +2767,7 @@
         <v>84</v>
       </c>
       <c r="D78" s="2">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="79" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -2781,7 +2781,7 @@
         <v>85</v>
       </c>
       <c r="D79" s="3">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="80" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3089,7 +3089,7 @@
         <v>107</v>
       </c>
       <c r="D101" s="3">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3117,7 +3117,7 @@
         <v>111</v>
       </c>
       <c r="D103" s="3">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3243,7 +3243,7 @@
         <v>120</v>
       </c>
       <c r="D112" s="2">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3439,7 +3439,7 @@
         <v>134</v>
       </c>
       <c r="D126" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="127" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3509,7 +3509,7 @@
         <v>139</v>
       </c>
       <c r="D131" s="3">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="132" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3929,7 +3929,7 @@
         <v>171</v>
       </c>
       <c r="D161" s="3">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="162" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3985,7 +3985,7 @@
         <v>175</v>
       </c>
       <c r="D165" s="3">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="166" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -4363,7 +4363,7 @@
         <v>202</v>
       </c>
       <c r="D192" s="2">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="193" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -4503,7 +4503,7 @@
         <v>214</v>
       </c>
       <c r="D202" s="2">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="203" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -4685,7 +4685,7 @@
         <v>227</v>
       </c>
       <c r="D215" s="3">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="216" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -4797,7 +4797,7 @@
         <v>235</v>
       </c>
       <c r="D223" s="3">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="224" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -4909,7 +4909,7 @@
         <v>243</v>
       </c>
       <c r="D231" s="3">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="232" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -5343,7 +5343,7 @@
         <v>276</v>
       </c>
       <c r="D262" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="263" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -5455,7 +5455,7 @@
         <v>284</v>
       </c>
       <c r="D270" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="271" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -5567,7 +5567,7 @@
         <v>292</v>
       </c>
       <c r="D278" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="279" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -5581,7 +5581,7 @@
         <v>293</v>
       </c>
       <c r="D279" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="280" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6267,7 +6267,7 @@
         <v>342</v>
       </c>
       <c r="D328" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="329" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6337,7 +6337,7 @@
         <v>347</v>
       </c>
       <c r="D333" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="334" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6771,7 +6771,7 @@
         <v>378</v>
       </c>
       <c r="D364" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="365" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6995,7 +6995,7 @@
         <v>394</v>
       </c>
       <c r="D380" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="381" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
